--- a/Funding_impactAnalysis/data/subcounties_usedHivsyphilsdual.xlsx
+++ b/Funding_impactAnalysis/data/subcounties_usedHivsyphilsdual.xlsx
@@ -14,670 +14,670 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="222">
   <si>
-    <t xml:space="preserve">county_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sub_county_name</t>
+    <t xml:space="preserve">County</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sub county</t>
   </si>
   <si>
     <t xml:space="preserve">Baringo County</t>
   </si>
   <si>
-    <t xml:space="preserve">Baringo Central Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baringo North Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marigat Sub County</t>
+    <t xml:space="preserve">baringo central</t>
+  </si>
+  <si>
+    <t xml:space="preserve">baringo north</t>
+  </si>
+  <si>
+    <t xml:space="preserve">marigat</t>
   </si>
   <si>
     <t xml:space="preserve">Bomet County</t>
   </si>
   <si>
-    <t xml:space="preserve">Bomet Central Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bomet East Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chepalungu Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Konoin Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sotik Sub County</t>
+    <t xml:space="preserve">bomet central</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bomet east</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chepalungu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">konoin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sotik</t>
   </si>
   <si>
     <t xml:space="preserve">Bungoma County</t>
   </si>
   <si>
-    <t xml:space="preserve">Bumula Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cheptais Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kabuchai Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kanduyi Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kimilili Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mt Elgon Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sirisia Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Webuye East Sub County</t>
+    <t xml:space="preserve">bumula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cheptais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kabuchai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kanduyi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kimilili</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mt elgon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sirisia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">webuye east</t>
   </si>
   <si>
     <t xml:space="preserve">Busia County</t>
   </si>
   <si>
-    <t xml:space="preserve">Bunyala Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Butula Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matayos Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nambale Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teso Central Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teso South Sub County</t>
+    <t xml:space="preserve">bunyala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">butula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">matayos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nambale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">teso central</t>
+  </si>
+  <si>
+    <t xml:space="preserve">teso south</t>
   </si>
   <si>
     <t xml:space="preserve">Elgeyo Marakwet County</t>
   </si>
   <si>
-    <t xml:space="preserve">Keiyo North Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marakwet East Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marakwet West Sub County</t>
+    <t xml:space="preserve">keiyo north</t>
+  </si>
+  <si>
+    <t xml:space="preserve">marakwet east</t>
+  </si>
+  <si>
+    <t xml:space="preserve">marakwet west</t>
   </si>
   <si>
     <t xml:space="preserve">Embu County</t>
   </si>
   <si>
-    <t xml:space="preserve">Embu North Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Embu west Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mbeere North Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mbeere South Sub County</t>
+    <t xml:space="preserve">embu north</t>
+  </si>
+  <si>
+    <t xml:space="preserve">embu west</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mbeere north</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mbeere south</t>
   </si>
   <si>
     <t xml:space="preserve">Homa Bay County</t>
   </si>
   <si>
-    <t xml:space="preserve">Rachuonyo East Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rachuonyo North  Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suba North Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suba South Sub County</t>
+    <t xml:space="preserve">rachuonyo east</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rachuonyo north</t>
+  </si>
+  <si>
+    <t xml:space="preserve">suba north</t>
+  </si>
+  <si>
+    <t xml:space="preserve">suba south</t>
   </si>
   <si>
     <t xml:space="preserve">Kajiado County</t>
   </si>
   <si>
-    <t xml:space="preserve">Kajiado Central Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kajiado East Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kajiado North Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loitokitok Sub County</t>
+    <t xml:space="preserve">kajiado central</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kajiado east</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kajiado north</t>
+  </si>
+  <si>
+    <t xml:space="preserve">loitokitok</t>
   </si>
   <si>
     <t xml:space="preserve">Kakamega County</t>
   </si>
   <si>
-    <t xml:space="preserve">Butere Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ikolomani Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Khwisero Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Likuyani Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lurambi Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malava Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matungu Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mumias West Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Navakholo Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shinyalu Sub County</t>
+    <t xml:space="preserve">butere</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ikolomani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">khwisero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">likuyani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lurambi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">malava</t>
+  </si>
+  <si>
+    <t xml:space="preserve">matungu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mumias west</t>
+  </si>
+  <si>
+    <t xml:space="preserve">navakholo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">shinyalu</t>
   </si>
   <si>
     <t xml:space="preserve">Kericho County</t>
   </si>
   <si>
-    <t xml:space="preserve">Ainamoi Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bureti Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kipkelion West Sub County</t>
+    <t xml:space="preserve">ainamoi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bureti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kipkelion west</t>
   </si>
   <si>
     <t xml:space="preserve">Kiambu County</t>
   </si>
   <si>
-    <t xml:space="preserve">Githunguri Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kikuyu Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lari Sub County</t>
+    <t xml:space="preserve">githunguri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kikuyu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lari</t>
   </si>
   <si>
     <t xml:space="preserve">Kilifi County</t>
   </si>
   <si>
-    <t xml:space="preserve">Ganze Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaloleni Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kilifi North Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kilifi South Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magarini Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malindi Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rabai Sub County</t>
+    <t xml:space="preserve">ganze</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kaloleni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kilifi north</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kilifi south</t>
+  </si>
+  <si>
+    <t xml:space="preserve">magarini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">malindi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rabai</t>
   </si>
   <si>
     <t xml:space="preserve">Kirinyaga County</t>
   </si>
   <si>
-    <t xml:space="preserve">Kirinyaga Central Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kirinyaga East Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kirinyaga North/Mwea West Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kirinyaga West Sub County</t>
+    <t xml:space="preserve">kirinyaga central</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kirinyaga east</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kirinyaga north/mwea west</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kirinyaga west</t>
   </si>
   <si>
     <t xml:space="preserve">Kisii County</t>
   </si>
   <si>
-    <t xml:space="preserve">Bomachoge Chache Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bonchari Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kitutu Chache North Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kitutu Chache South Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nyaribari Chache Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nyaribari Masaba Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">South Mugirango Sub County</t>
+    <t xml:space="preserve">bomachoge chache</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bonchari</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kitutu chache north</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kitutu chache south</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nyaribari chache</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nyaribari masaba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">south mugirango</t>
   </si>
   <si>
     <t xml:space="preserve">Kisumu County</t>
   </si>
   <si>
-    <t xml:space="preserve">Kadibo Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kisumu Central Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kisumu East Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kisumu West Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Muhoroni Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nyando Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seme Sub County</t>
+    <t xml:space="preserve">kadibo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kisumu central</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kisumu east</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kisumu west</t>
+  </si>
+  <si>
+    <t xml:space="preserve">muhoroni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nyando</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seme</t>
   </si>
   <si>
     <t xml:space="preserve">Kitui County</t>
   </si>
   <si>
-    <t xml:space="preserve">Kitui Central Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kitui East Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kitui Rural Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kitui South Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kitui West Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mwingi Central Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mwingi North Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mwingi West Sub County</t>
+    <t xml:space="preserve">kitui central</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kitui east</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kitui rural</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kitui south</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kitui west</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mwingi central</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mwingi north</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mwingi west</t>
   </si>
   <si>
     <t xml:space="preserve">Laikipia County</t>
   </si>
   <si>
-    <t xml:space="preserve">Laikipia East Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laikipia North Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laikipia West Sub County</t>
+    <t xml:space="preserve">laikipia east</t>
+  </si>
+  <si>
+    <t xml:space="preserve">laikipia north</t>
+  </si>
+  <si>
+    <t xml:space="preserve">laikipia west</t>
   </si>
   <si>
     <t xml:space="preserve">Machakos County</t>
   </si>
   <si>
-    <t xml:space="preserve">Athi River Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kalama Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kangundo Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Machakos Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Masinga Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matungulu Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mwala Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yatta Sub County</t>
+    <t xml:space="preserve">athi river</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kalama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kangundo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">machakos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">masinga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">matungulu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mwala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yatta</t>
   </si>
   <si>
     <t xml:space="preserve">Makueni County</t>
   </si>
   <si>
-    <t xml:space="preserve">Kaiti Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Makueni Sub County</t>
+    <t xml:space="preserve">kaiti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">makueni</t>
   </si>
   <si>
     <t xml:space="preserve">Marsabit County</t>
   </si>
   <si>
-    <t xml:space="preserve">North Horr Sub County</t>
+    <t xml:space="preserve">north horr</t>
   </si>
   <si>
     <t xml:space="preserve">Meru County</t>
   </si>
   <si>
-    <t xml:space="preserve">Igembe North Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imenti Central Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tigania West Sub County</t>
+    <t xml:space="preserve">igembe north</t>
+  </si>
+  <si>
+    <t xml:space="preserve">imenti central</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tigania west</t>
   </si>
   <si>
     <t xml:space="preserve">Migori County</t>
   </si>
   <si>
-    <t xml:space="preserve">Awendo Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kuria East Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kuria West Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nyatike Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rongo Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suna East Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suna West Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uriri Sub County</t>
+    <t xml:space="preserve">awendo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kuria east</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kuria west</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nyatike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rongo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">suna east</t>
+  </si>
+  <si>
+    <t xml:space="preserve">suna west</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uriri</t>
   </si>
   <si>
     <t xml:space="preserve">Mombasa County</t>
   </si>
   <si>
-    <t xml:space="preserve">Changamwe Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jomvu Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Likoni Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mvita Sub County</t>
+    <t xml:space="preserve">changamwe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jomvu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">likoni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mvita</t>
   </si>
   <si>
     <t xml:space="preserve">Nairobi County</t>
   </si>
   <si>
-    <t xml:space="preserve">Dagoretti South Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Embakasi Central Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Embakasi South Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Embakasi West Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kamukunji Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kasarani Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mathare Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roysambu Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ruaraka Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Starehe Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Westlands Sub County</t>
+    <t xml:space="preserve">dagoretti south</t>
+  </si>
+  <si>
+    <t xml:space="preserve">embakasi central</t>
+  </si>
+  <si>
+    <t xml:space="preserve">embakasi south</t>
+  </si>
+  <si>
+    <t xml:space="preserve">embakasi west</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kamukunji</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kasarani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mathare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">roysambu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ruaraka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">starehe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">westlands</t>
   </si>
   <si>
     <t xml:space="preserve">Nakuru County</t>
   </si>
   <si>
-    <t xml:space="preserve">Gilgil Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kuresoi North Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Molo Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Naivasha Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nakuru East Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nakuru North Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nakuru West Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Njoro Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rongai Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Subukia Sub County</t>
+    <t xml:space="preserve">gilgil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kuresoi north</t>
+  </si>
+  <si>
+    <t xml:space="preserve">molo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">naivasha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nakuru east</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nakuru north</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nakuru west</t>
+  </si>
+  <si>
+    <t xml:space="preserve">njoro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rongai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">subukia</t>
   </si>
   <si>
     <t xml:space="preserve">Nandi County</t>
   </si>
   <si>
-    <t xml:space="preserve">Aldai Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chesumei Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Emgwen Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mosop Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tinderet Sub County</t>
+    <t xml:space="preserve">aldai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chesumei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emgwen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mosop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tinderet</t>
   </si>
   <si>
     <t xml:space="preserve">Narok County</t>
   </si>
   <si>
-    <t xml:space="preserve">Narok Central Sub County</t>
+    <t xml:space="preserve">narok central</t>
   </si>
   <si>
     <t xml:space="preserve">Nyandarua County</t>
   </si>
   <si>
-    <t xml:space="preserve">Kinangop Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ndaragwa Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oljoroorok Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Olkalou Sub County</t>
+    <t xml:space="preserve">kinangop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ndaragwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">oljoroorok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">olkalou</t>
   </si>
   <si>
     <t xml:space="preserve">Samburu County</t>
   </si>
   <si>
-    <t xml:space="preserve">Samburu Central Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samburu East Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samburu North Sub County</t>
+    <t xml:space="preserve">samburu central</t>
+  </si>
+  <si>
+    <t xml:space="preserve">samburu east</t>
+  </si>
+  <si>
+    <t xml:space="preserve">samburu north</t>
   </si>
   <si>
     <t xml:space="preserve">Siaya County</t>
   </si>
   <si>
-    <t xml:space="preserve">Alego Usonga Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bondo Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gem Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rarieda Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ugenya Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ugunja Sub County</t>
+    <t xml:space="preserve">alego usonga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bondo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rarieda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ugenya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ugunja</t>
   </si>
   <si>
     <t xml:space="preserve">Taita Taveta County</t>
   </si>
   <si>
-    <t xml:space="preserve">Mwatate Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voi Sub County</t>
+    <t xml:space="preserve">mwatate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">voi</t>
   </si>
   <si>
     <t xml:space="preserve">Tharaka Nithi County</t>
   </si>
   <si>
-    <t xml:space="preserve">Chuka Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Igambangombe Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maara Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Muthambi Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tharaka North Sub County</t>
+    <t xml:space="preserve">chuka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">igambangombe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maara</t>
+  </si>
+  <si>
+    <t xml:space="preserve">muthambi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tharaka north</t>
   </si>
   <si>
     <t xml:space="preserve">Trans Nzoia County</t>
   </si>
   <si>
-    <t xml:space="preserve">Cherangany Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Endebess Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kiminini Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kwanza Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saboti Sub County</t>
+    <t xml:space="preserve">cherangany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">endebess</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kiminini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kwanza</t>
+  </si>
+  <si>
+    <t xml:space="preserve">saboti</t>
   </si>
   <si>
     <t xml:space="preserve">Turkana County</t>
   </si>
   <si>
-    <t xml:space="preserve">Aroo Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loima Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lokichoggio Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turkana Central Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turkana East Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turkana South Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turkana West Sub County</t>
+    <t xml:space="preserve">aroo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">loima</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lokichoggio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">turkana central</t>
+  </si>
+  <si>
+    <t xml:space="preserve">turkana east</t>
+  </si>
+  <si>
+    <t xml:space="preserve">turkana south</t>
+  </si>
+  <si>
+    <t xml:space="preserve">turkana west</t>
   </si>
   <si>
     <t xml:space="preserve">Uasin Gishu County</t>
   </si>
   <si>
-    <t xml:space="preserve">Ainabkoi Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kapseret Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kesses Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soy Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turbo Sub County</t>
+    <t xml:space="preserve">ainabkoi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kapseret</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kesses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">soy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">turbo</t>
   </si>
   <si>
     <t xml:space="preserve">Vihiga County</t>
   </si>
   <si>
-    <t xml:space="preserve">Emuhaya Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hamisi Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luanda Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sabatia Sub County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vihiga Sub County</t>
+    <t xml:space="preserve">emuhaya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hamisi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">luanda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sabatia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vihiga</t>
   </si>
 </sst>
 </file>

--- a/Funding_impactAnalysis/data/subcounties_usedHivsyphilsdual.xlsx
+++ b/Funding_impactAnalysis/data/subcounties_usedHivsyphilsdual.xlsx
@@ -68,7 +68,7 @@
     <t xml:space="preserve">kimilili</t>
   </si>
   <si>
-    <t xml:space="preserve">mt elgon</t>
+    <t xml:space="preserve">mt. elgon</t>
   </si>
   <si>
     <t xml:space="preserve">sirisia</t>
@@ -194,7 +194,7 @@
     <t xml:space="preserve">ainamoi</t>
   </si>
   <si>
-    <t xml:space="preserve">bureti</t>
+    <t xml:space="preserve">buret</t>
   </si>
   <si>
     <t xml:space="preserve">kipkelion west</t>
@@ -341,7 +341,7 @@
     <t xml:space="preserve">Machakos County</t>
   </si>
   <si>
-    <t xml:space="preserve">athi river</t>
+    <t xml:space="preserve">mavoko</t>
   </si>
   <si>
     <t xml:space="preserve">kalama</t>
@@ -386,7 +386,7 @@
     <t xml:space="preserve">igembe north</t>
   </si>
   <si>
-    <t xml:space="preserve">imenti central</t>
+    <t xml:space="preserve">cental imenti</t>
   </si>
   <si>
     <t xml:space="preserve">tigania west</t>
@@ -485,13 +485,13 @@
     <t xml:space="preserve">naivasha</t>
   </si>
   <si>
-    <t xml:space="preserve">nakuru east</t>
+    <t xml:space="preserve">nakuru town east</t>
   </si>
   <si>
     <t xml:space="preserve">nakuru north</t>
   </si>
   <si>
-    <t xml:space="preserve">nakuru west</t>
+    <t xml:space="preserve">nakuru town west</t>
   </si>
   <si>
     <t xml:space="preserve">njoro</t>
@@ -536,10 +536,10 @@
     <t xml:space="preserve">ndaragwa</t>
   </si>
   <si>
-    <t xml:space="preserve">oljoroorok</t>
-  </si>
-  <si>
-    <t xml:space="preserve">olkalou</t>
+    <t xml:space="preserve">ol jorok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ol kalou</t>
   </si>
   <si>
     <t xml:space="preserve">Samburu County</t>
